--- a/docs/DS粗灰-方向与水平验证结论.xlsx
+++ b/docs/DS粗灰-方向与水平验证结论.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="结论" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="三切分验证明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="落地与待办" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="真向前验证" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="方向验证明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="数据导入-20260924" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="备选方案-4因子" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="落地与待办" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -98,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -120,6 +123,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -487,19 +496,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DS 粗精煤泥灰分：水平值不可用、方向可用（2026-09-23 验证结论）</t>
+          <t>DS 粗精煤泥灰分：水平值不可用、方向可用（2026-09-24 用 205 条数据复核）</t>
         </is>
       </c>
     </row>
@@ -538,12 +547,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>锁死检验集（8-9 月 39 条）上：DS 基线 MAE 2.652、加滞后 2.628、持续性 3.244、增量模型 14.340；而「取开发集均值」基线 MAE 2.263 —— 所有候选都输给均值基线。</t>
+          <t>锁定检验窗（训练 6-16~9-03 共 155 条 → 检验 9-04~9-21 共 50 条，模型没见过）：模型(4因子(原煤灰/煤量/液位/水分)|MLR) MAE 1.521，而「取训练均值」MAE 1.744、最强在线基线（在线·EWMA0.2）MAE 1.549。</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>原因不是算法：灰分中枢跨期漂移（6-7 月约 14.0、8-9 月约 14.9），水平外推必然被系统性偏移拖死。因此 DS 的水平输出只能标注为「历史对照」。</t>
+          <t>原因不是算法，而是灰分中枢跨期漂移：本窗训练期均值 14.209、检验期均值 13.400（-0.809）。因此 DS 水平输出只能标注为「历史对照」，不能当向前精度承诺。</t>
         </is>
       </c>
     </row>
@@ -560,12 +569,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>「第 t 条已知信息 → 第 t+1 条相对第 t 条涨跌」：三个切分点命中 0.771（6-7→8-9，区间 [0.629,0.914]，n=35）、0.727（6→7，[0.591,0.841]，n=44）、0.617（6→7+8+9，[0.506,0.716]，n=81）。多数基线 0.514~0.531。</t>
+          <t>新独立窗口（切点 2026-09-04）：命中 0.762，多数基线 0.524、惯性基线 0.214，95% 区间 [0.643, 0.881]，n=42。更早的切点 2026-08-23：命中 0.667（区间 [0.564, 0.769]，n=78）；旧月切口径 0.667（n=78）。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>验收门槛：bootstrap 95% 区间**下界 &gt; 多数基线** 才判可用。第三个切分因此被正确拒绝 —— 门控不是橡皮图章。</t>
+          <t>验收门槛：bootstrap 95% 区间**下界 &gt; max(多数基线, 惯性基线)** 才判可用。方向用「第 t 条已知信息」预测「第 t+1 条相对第 t 条的涨跌」，|Δ|≤0.5% 记为平、不计入命中。</t>
         </is>
       </c>
     </row>
@@ -582,56 +591,100 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>惯性基线（本次涨→下次继续涨）仅 0.343（明显反持续）；去掉「到下次读数的时间间隔」特征后，三个切分命中率不变（0.727/0.771/0.771）。</t>
+          <t>惯性基线（本次涨→下次继续涨）仅 0.214，明显反持续；去掉「到下次读数的时间间隔」特征后命中率不变。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>模型从「Δprev + prev 水平」重建当前水平，当前偏高则下次多半回落。正式版**不使用**时间间隔特征 —— 排除「靠采样节奏猜方向」的偏利。</t>
+          <t>模型从「Δprev + 上一条水平」重建当前水平：当前偏高则下次多半回落。正式版**不使用**时间间隔特征 —— 排除「靠采样节奏猜方向」的偏利。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
+          <t>拟合度的陷阱</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>拟合度高 ≠ 向前可用（本轮又验了一次）</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>同一锁定窗：把目标换成「灰分−原煤灰」后，样本内 R² 从 0.374 升到 0.754，而向前 MAE 从 1.814 恶化到 1.939。</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>所以系统里把「样本内 R²」与「向前 MAE + 基线对照」并列展示，选型只看向前窗口。（0.754/1.939 为目标变换实验值，见「备选方案-4因子」表同批实验。）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>工程结论</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>把向前验证做成常规数字（已落地）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>新增只读接口 GET /api/v1/training/coarse-forward（返回向前 MAE、朴素基线、方向命中与门控结论），DS 训练结果同时带 forward 与 direction；粗精煤泥页 DS 视图直接显示该区块。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>接口只读、不训练、不写库；结果按 (数据指纹, range) 进程内缓存，首次约 4~8 秒、之后即时。训练范围若选「全部」，没有剩余数据可检验 → 页面显示「留尾参考」并说明原因。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>纪律①（踩过坑）</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>特征只能用 t 时刻**已知**量</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>曾把「第 t 条自身的灰分同源测量」与「第 t 条自身的变化」配对，得到 0.833~0.917 的假命中率；把目标前移一格（真向前）后掉到 0.657~0.771。</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>前者是「同时刻解释」——生产上第 t 条还不存在，等于用未来信息。这条假象已写进模块文档，作为反面教材保留。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>前者是「同时刻解释」——生产上第 t 条还不存在，等于用未来信息。这条假象写进模块文档作反面教材。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>纪律②（对称的）</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>也不能只追某个前向指标</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>增量模型的向前 q2Time = +0.417（看着很好），但其检验集 R² = −11.47、MAE = 14.34 —— 彻底崩。</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>原因：目标换成 Δ 后 Q² 是在「增量方差」上算的，量纲与水平值不同，跨口径比指标会得出相反结论。任何前向指标必须与「水平 MAE / 是否打赢均值基线」一起看。</t>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>目标换成 Δ 后 Q² 是在「增量方差」上算的，量纲与水平值不同，跨口径比指标会得出相反结论。任何前向指标必须与「水平 MAE / 是否打赢均值基线」一起看。</t>
         </is>
       </c>
     </row>
@@ -649,220 +702,1049 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>方向信号稳健性：三切分 × 两特征组（Ridge 回归 Δ 取符号，|Δ|&gt;0.5% 计入）</t>
+          <t>真向前验收：训练只用切点之前、评估只用切点之后（2026-09-24 现算，库内粗灰 205 条）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>切分</t>
+          <t>窗口</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>特征组</t>
+          <t>对象</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>方向命中</t>
+          <t>训练n</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>多数基线</t>
+          <t>检验n</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>95% bootstrap</t>
+          <t>训练截止 / 检验区间</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>检验样本</t>
+          <t>向前 MAE</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>门控结论</t>
+          <t>偏差</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>6-7月 → 8-9月</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>full（含间隔）</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>[0.629, 0.914]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>可用</t>
-        </is>
-      </c>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据）</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>（窗口概览）</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>训练 →2026-09-03（均值 14.209）｜检验 2026-09-04 ~ 2026-09-21（均值 13.400）</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>6-7月 → 8-9月</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>nogap（正式版）</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>[0.629, 0.914]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>可用</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 模型</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>4因子(原煤灰/煤量/液位/水分)|MLR</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.521</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.690</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.324｜向前 R² +0.155</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>6月 → 7月</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>[0.591, 0.841]</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>可用</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 模型</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>4因子(原煤灰/煤量/液位/水分)|PLS</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.552</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.673</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.327｜向前 R² +0.131</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>6月 → 7月</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>nogap（正式版）</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>[0.591, 0.841]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>可用</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 模型</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>10因子(现行)|MLR</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.814</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.961</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.374｜向前 R² -0.216</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>6月 → 7+8+9月</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>nogap</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>[0.506, 0.716]</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>拒绝（下界未超基线）</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 模型</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>10因子(现行)|PLS</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.847</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.872</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.367｜向前 R² -0.203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 基线</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>在线·EWMA0.2</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.549</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.004</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.134</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 基线</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>在线·近5条均值</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.568</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.006</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.175</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 基线</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>在线·近20条均值</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.589</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.018</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.078</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 基线</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>取训练均值</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.744</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.809</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.134</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 基线</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>在线·近1条均值</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.444</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.003</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -1.331</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>锁定检验窗（9-04~9-21，新数据） · 方向</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>下一读数涨跌</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr"/>
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>命中 0.762</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>多数基线 0.524｜惯性 0.214</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>95%区间 [0.643, 0.881]，n=42，可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03）</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>（窗口概览）</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>训练 →2026-07-14（均值 14.045）｜检验 2026-08-23 ~ 2026-09-03（均值 14.649）</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 模型</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>4因子(原煤灰/煤量/液位/水分)|MLR</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.413</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.608</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.475｜向前 R² -0.412</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 模型</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>4因子(原煤灰/煤量/液位/水分)|PLS</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.524</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.579</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.479｜向前 R² -0.501</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 模型</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>10因子(现行)|MLR</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr"/>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.564</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.089</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.538｜向前 R² -0.432</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 模型</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>10因子(现行)|PLS</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr"/>
+      <c r="D19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.607</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.108</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.530｜向前 R² -0.512</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 基线</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>取训练均值</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.095</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>偏差 -0.604</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.048</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 基线</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>在线·近20条均值</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr"/>
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.137</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.592</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 基线</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>在线·EWMA0.2</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr"/>
+      <c r="D22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.219</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.344</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.069</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 基线</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>在线·近5条均值</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.334</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.232</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.114</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 基线</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>在线·近1条均值</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.917</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.035</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -1.113</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>开发侧向前窗（8-23~9-03） · 方向</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>下一读数涨跌</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>命中 0.667</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>多数基线 0.500｜惯性 0.269</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>95%区间 [0.564, 0.769]，n=78，可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21）</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>（窗口概览）</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>训练 →2026-07-14（均值 14.045）｜检验 2026-08-23 ~ 2026-09-21（均值 13.970）</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 模型</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>4因子(原煤灰/煤量/液位/水分)|MLR</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr"/>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.007</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.029</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.475｜向前 R² -0.145</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 模型</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>4因子(原煤灰/煤量/液位/水分)|PLS</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.100</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.042</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.479｜向前 R² -0.219</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 模型</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>10因子(现行)|MLR</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr"/>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.250</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.381</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.538｜向前 R² -0.332</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 模型</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>10因子(现行)|PLS</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr"/>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.308</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.433</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 0.530｜向前 R² -0.379</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 基线</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>在线·近20条均值</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr"/>
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.839</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.260</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² +0.017</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 基线</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>在线·EWMA0.2</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr"/>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.855</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.155</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.032</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 基线</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>取训练均值</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr"/>
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.861</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.075</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 基线</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>在线·近5条均值</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr"/>
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>MAE 1.917</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.103</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -0.073</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 基线</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>在线·近1条均值</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr"/>
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>MAE 2.660</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>偏差 +0.018</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>向前 R² -1.076</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>部署口径 jun_jul 留出整段（8-23~9-21） · 方向</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>下一读数涨跌</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr"/>
+      <c r="D36" s="10" t="inlineStr"/>
+      <c r="E36" s="10" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>命中 0.667</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>多数基线 0.500｜惯性 0.269</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>95%区间 [0.564, 0.769]，n=78，可用</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -874,217 +1756,955 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>已完成 / 待做 / 现场待确认</t>
+          <t>方向信号稳健性：不同切分 × 门控结论（Ridge 回归 Δ 取符号，|Δ|&gt;0.5% 计入）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>切分口径</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>开发 / 检验</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>方向命中</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>多数基线</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>惯性基线</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>95% bootstrap</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>检验样本</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>门控结论</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>coarse_direction.py</t>
+          <t>时间切分 2026-09-04（新数据）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>方向判断模块：direction_report() 输出 usable/hit/baseline/ci/n/note/gating，自带 CLI 自检；两条纪律写进模块文档。</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>已提交 3b48f09</t>
+          <t>6-16~9-03 / 9-04~9-21（50 条）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>[0.643, 0.881]</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>可用</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>单元测试</t>
+          <t>时间切分 2026-08-23</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>3 条：均值回复序列必须判可用；**随机游走必须判不可用**（锁住门控）；报告必须声明 gating。</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>3 passed</t>
+          <t>6-16~8-22 / 8-23~9-21</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>[0.564, 0.769]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>可用</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>接入训练编排</t>
+          <t>月份切分（旧口径）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>DS 训练结束时调用 direction_report()，作为新键 direction 返回；开发月=本次实际训练月份、检验月=不在开发月的最后两个月；异常隔离不影响主训练。</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>已提交 2f6f9d1</t>
+          <t>2026-06+07 / 2026-08+09</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>[0.564, 0.769]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>可用</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>对拍基线</t>
+          <t>月份切分（2026-09-23 首版）</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>不需要动</t>
+          <t>2026-06+07 / 2026-08+09（当时 152 条）</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>[0.629, 0.914]</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>月份切分（首版第二组）</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06 / 2026-07</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>[0.591, 0.841]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>月份切分（首版被拒的那组）</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06 / 2026-07+08+09</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>[0.506, 0.716]</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>拒绝（下界未超基线）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>新数据导入（用户 2026-09-24 确认口径后执行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>依据 / 结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>源文件</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>C:\Users\25925\Desktop\web(2)导入数据\新 下的 3 个文件：粗精煤泥灰分影响因素9-23.xlsx、灰分、密度 （导入版)9-23.xlsx、浮精 (1)9-23.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>旧版本文件（9-4 系列）与 ~$ 锁定文件不导；导入前确认工作簿已关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>粗精煤泥</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>**有效数据只有 61 行**（3 行表头之外其余为空）→ 不再做日期向下填充，只导这 61 行；库内粗灰 152 → 205 条，覆盖延到 2026-09-21</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>用户 2026-09-24 明确：其余为空、只导有效行</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>灰分密度</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>**只导 A 系统** 183 行（B 系统 183 行不导并在 import_logs.errors 留痕）；A 系统里密度写 1 的 6 行仍导入、密度记 NULL（保住灰分）</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>用户口径「只导A」；与前端导入页 import.js 对坏密度的处理一致；库内 360 → 543 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>浮精</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>14 行（9-04~9-20），库内 17 → 31 条</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>煤量须在 0~60 t/h；本批无异常行</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>9-01/9-02 重叠</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>新文件与库内旧数据是同一天同批采样、时间与数值都不同（旧值来自 9-5 的『9-4』文件）→ **以新文件为准**：删库内 8 行、写入新文件 9 行（净 +1）</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>用户 2026-09-24 选择「以新文件为准」；脚本 --overlap replace，重叠判定窗口 60 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>写入方式与安全</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>单事务写入；写入前用 sqlite3 在线备份 API 存 backups/dense_medium-preimport-newbatch-20260924-150607-498.db（385024 字节）</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>导入后核对：integrity_check=ok、同类无重复时间戳、条数 205/31/543、import_logs 新增 3 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>脚本</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>backend/scripts/import_new_batch.py（支持 --dry-run / --ash-systems / --overlap）</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>可重复执行：已存在的时间戳不会重复写入</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>未导入但保留的原始信息</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>B 系统 183 行里 76 行带真实密度值（与 A 差中位 0.007、最大 0.102）；9-08 08:33~13:33 有 6 个时刻只有 B 有密度</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>按「只导A」口径未导入；如需补导，重跑脚本加 --ash-systems A,B 即可（不会破坏 A 行）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>备选：去掉 6 个接近常量的开关列（**未采用**，用户 2026-09-24 决定模型先不动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>特征集 / 口径</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>开发侧向前窗 MAE</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>锁定检验窗 MAE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>样本内 R²（锁定窗）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>10 因子（现行）</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>2.564</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>1.814</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>0.374</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>sysA/sysB/sys401/sys402/脱粉473/474 六个开关列在样本里几乎不变（sysA 均值 0.97），对向前预测只贡献噪声</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>4 因子（原煤灰/煤量/液位/水分）</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>2.413</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>1.521</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>0.324</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>两个窗口一致更优（锁定窗显著：配对 bootstrap 差值区间 [+0.138, +0.643] 不含 0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>目标变换（灰分−原煤灰）</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>2.633</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>1.939</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>0.754</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>样本内 R² 最漂亮、向前最差之一 —— 只追拟合度会选错模型</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>目标变换（灰分/原煤灰）</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>2.488</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>1.821</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>0.459</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>同上，向前没有改善</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>已完成 / 待做 / 现场待确认（2026-09-24）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>coarse_direction.py</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>方向判断模块：direction_report() 输出 usable/hit/baseline/inertia/ci/n/note/gating，支持 split_ts 时间切分与月份切分；自带 CLI 自检。</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>已提交 3b48f09</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>单元测试</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>方向 3 条（均值回复必须可用 / 随机游走必须拒绝 / 必须声明 gating）+ 向前验证 6 条（store 键兼容、split_ts、leftover 与 tail、缓存、训练结果携带）。</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>9 passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>时间切分修复</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>按月份切分在「训练范围已覆盖最新月份」时会把检验集切成空集（2026-09-24 实际发生）；改为按时间点切分 split_ts，并修掉只认 `ts` 键导致训练路径恒返回「样本不足」的缺陷。</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>已修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>真向前服务</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>direction 只进 HTTP 响应，不进 metrics/history/保存快照 → DS 基线 train_js.json 无需重生成（对拍测试保持通过即为证据）。</t>
+          <t>app/services/coarse_forward.py：只读评估（模型 + 取训练均值/在线近k条/EWMA 基线 + 方向），训练范围之后为 leftover 口径、覆盖全部时退化为 tail 留尾并说明。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>已验证</t>
+          <t>本次</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>只读接口</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>GET /api/v1/training/coarse-forward?range=&amp;engine=ds[&amp;sets=1]；进程内按数据指纹缓存，首次约 4~8 秒。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>本次</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>训练结果</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>DS 训练返回 forward（真向前 MAE/基线/结论文字）与 direction；随模型快照一起存档。只加新键、不动 mlr/pls/metrics/history → DS 对拍基线 train_js.json 无需重生成。</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>本次</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>前端展示</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>待做</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>粗精煤泥页新增「下一读数方向：偏涨/偏跌（历史命中 0.77，区间 0.63~0.91）」；水平值栏在 direction.usable=false 时标注「仅历史对照」。需要把 direction 透出到保存快照与 /state 兼容模型 → 会牵动对拍基线，需一并重生成并跑对拍。</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>文档并表</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>待做</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>本结论后续并入 docs/待办-后续优化计划.xlsx（按编号关联，避免重复 Sheet）。</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>瞬时值前提</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>待现场确认</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>本结论建立在「粗精煤泥信息表全是瞬时值、无人为采样」之上（用户 2026-09-23 说明）；若其中含人为填报/班次加权值，需复核方向结论。</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>粗精煤泥页 DS 视图新增「向前验证」区块：训练窗/检验窗、模型向前 MAE 与最强朴素基线、方向命中与区间、样本内 R² 提示；训练范围为 all 时标注「留尾参考」。</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>本次</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>采样节奏</t>
+          <t>端到端验证</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>已知事实</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>37 天里每日 4~5 点，时刻集中在 00 时 / 07-10 时 / 21-23 时（白班 08-10 时一天 2~3 点）；相邻读数间隔中位 2.6 小时 —— 这是「水平值不可预测」的直接背景。</t>
+          <t>backend/scripts/verify_coarse_forward.js（对着临时库后端跑）：15 项断言，含页面与接口数字一致、留尾文案、旧后端降级提示。</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>已核实</t>
+          <t>15 passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>4 因子备选</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>待决策</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>去掉 6 个近常量开关列在两个窗口一致更优（锁定窗 MAE 1.814→1.521）。用户 2026-09-24 决定：模型先不动，只把向前验证与方向做进系统；本方案存档待更多数据。</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>待拍板</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>密度特征</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>数据缺口</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>想把「最近密度读数」作为因子：库内 A 系统密度读数只有 2026-05、08、09 三个月；6-7 月粗灰 113 条里 0 条能在 6 小时内对上密度读数 → **当前无法训练**。需要 PLC 密度连续采集接通后再评估。</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>待接入</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>旧后端一致性</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>生产 8000 仍跑 main 代码（无该接口）：页面检测到 404 时只显示一句灰字提示，不报红。</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>已降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>文档并表</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>待做</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>本结论后续按编号并入 docs/待办-后续优化计划.xlsx（避免重复 Sheet）。</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>现场待确认</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>B 系统 76 条真实密度是否补导；密度 1.441（9-21 单步降 0.079）是否手误；KEPServer 标签映射；P0 166 条是否收紧。</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>待确认</t>
         </is>
       </c>
     </row>
